--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.766024</v>
+        <v>0.626995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.476308</v>
+        <v>0.379168</v>
       </c>
       <c r="E2" t="n">
-        <v>0.91018</v>
+        <v>0.77646</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.865683</v>
+        <v>0.770159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.63929</v>
+        <v>0.457888</v>
       </c>
       <c r="E3" t="n">
-        <v>1.126038</v>
+        <v>1.015082</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.366273</v>
+        <v>0.281174</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2666</v>
+        <v>0.211414</v>
       </c>
       <c r="E4" t="n">
-        <v>0.649878</v>
+        <v>0.337498</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.571163</v>
+        <v>0.3315</v>
       </c>
       <c r="D5" t="n">
-        <v>0.339805</v>
+        <v>0.255239</v>
       </c>
       <c r="E5" t="n">
-        <v>0.996833</v>
+        <v>0.504512</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.626995</v>
+        <v>0.63491</v>
       </c>
       <c r="D2" t="n">
-        <v>0.379168</v>
+        <v>0.388335</v>
       </c>
       <c r="E2" t="n">
-        <v>0.77646</v>
+        <v>0.782212</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.770159</v>
+        <v>0.774709</v>
       </c>
       <c r="D3" t="n">
-        <v>0.457888</v>
+        <v>0.5132060000000001</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.281174</v>
+        <v>0.263819</v>
       </c>
       <c r="D4" t="n">
-        <v>0.211414</v>
+        <v>0.210006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.337498</v>
+        <v>0.343732</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3315</v>
+        <v>0.336378</v>
       </c>
       <c r="D5" t="n">
-        <v>0.255239</v>
+        <v>0.251422</v>
       </c>
       <c r="E5" t="n">
-        <v>0.504512</v>
+        <v>0.506674</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.63491</v>
+        <v>0.654959</v>
       </c>
       <c r="D2" t="n">
-        <v>0.388335</v>
+        <v>0.401948</v>
       </c>
       <c r="E2" t="n">
-        <v>0.782212</v>
+        <v>0.76535</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.774709</v>
+        <v>0.744555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5132060000000001</v>
+        <v>0.46057</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.263819</v>
+        <v>0.324485</v>
       </c>
       <c r="D4" t="n">
-        <v>0.210006</v>
+        <v>0.219982</v>
       </c>
       <c r="E4" t="n">
-        <v>0.343732</v>
+        <v>0.377377</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.336378</v>
+        <v>0.370963</v>
       </c>
       <c r="D5" t="n">
-        <v>0.251422</v>
+        <v>0.266822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.506674</v>
+        <v>0.607812</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.654959</v>
+        <v>0.67306</v>
       </c>
       <c r="D2" t="n">
-        <v>0.401948</v>
+        <v>0.409011</v>
       </c>
       <c r="E2" t="n">
-        <v>0.76535</v>
+        <v>0.780574</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.744555</v>
+        <v>0.742665</v>
       </c>
       <c r="D3" t="n">
-        <v>0.46057</v>
+        <v>0.530887</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.324485</v>
+        <v>0.321665</v>
       </c>
       <c r="D4" t="n">
-        <v>0.219982</v>
+        <v>0.211826</v>
       </c>
       <c r="E4" t="n">
-        <v>0.377377</v>
+        <v>0.37476</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.370963</v>
+        <v>0.3689</v>
       </c>
       <c r="D5" t="n">
-        <v>0.266822</v>
+        <v>0.274268</v>
       </c>
       <c r="E5" t="n">
-        <v>0.607812</v>
+        <v>0.606169</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.67306</v>
+        <v>0.673009</v>
       </c>
       <c r="D2" t="n">
-        <v>0.409011</v>
+        <v>0.40829</v>
       </c>
       <c r="E2" t="n">
-        <v>0.780574</v>
+        <v>0.774407</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.742665</v>
+        <v>0.741044</v>
       </c>
       <c r="D3" t="n">
-        <v>0.530887</v>
+        <v>0.528996</v>
       </c>
       <c r="E3" t="n">
         <v>1.015082</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.321665</v>
+        <v>0.243942</v>
       </c>
       <c r="D4" t="n">
-        <v>0.211826</v>
+        <v>0.18162</v>
       </c>
       <c r="E4" t="n">
-        <v>0.37476</v>
+        <v>0.337826</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3689</v>
+        <v>0.302208</v>
       </c>
       <c r="D5" t="n">
-        <v>0.274268</v>
+        <v>0.206256</v>
       </c>
       <c r="E5" t="n">
-        <v>0.606169</v>
+        <v>0.361551</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.673009</v>
+        <v>0.672434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.40829</v>
+        <v>0.35577</v>
       </c>
       <c r="E2" t="n">
-        <v>0.774407</v>
+        <v>0.76535</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.741044</v>
+        <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.528996</v>
+        <v>0.440642</v>
       </c>
       <c r="E3" t="n">
-        <v>1.015082</v>
+        <v>0.838984</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.243942</v>
+        <v>0.227718</v>
       </c>
       <c r="D4" t="n">
-        <v>0.18162</v>
+        <v>0.172775</v>
       </c>
       <c r="E4" t="n">
-        <v>0.337826</v>
+        <v>0.309013</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.302208</v>
+        <v>0.274223</v>
       </c>
       <c r="D5" t="n">
-        <v>0.206256</v>
+        <v>0.18748</v>
       </c>
       <c r="E5" t="n">
-        <v>0.361551</v>
+        <v>0.34293</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.227718</v>
+        <v>0.228795</v>
       </c>
       <c r="D4" t="n">
-        <v>0.172775</v>
+        <v>0.173719</v>
       </c>
       <c r="E4" t="n">
-        <v>0.309013</v>
+        <v>0.309272</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.274223</v>
+        <v>0.275792</v>
       </c>
       <c r="D5" t="n">
-        <v>0.18748</v>
+        <v>0.188319</v>
       </c>
       <c r="E5" t="n">
-        <v>0.34293</v>
+        <v>0.346301</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -473,7 +473,7 @@
         <v>0.672434</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35577</v>
+        <v>0.389014</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.440642</v>
+        <v>0.419404</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.228795</v>
+        <v>0.244684</v>
       </c>
       <c r="D4" t="n">
-        <v>0.173719</v>
+        <v>0.187885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.309272</v>
+        <v>0.309825</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.275792</v>
+        <v>0.277456</v>
       </c>
       <c r="D5" t="n">
-        <v>0.188319</v>
+        <v>0.209009</v>
       </c>
       <c r="E5" t="n">
-        <v>0.346301</v>
+        <v>0.374284</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.672434</v>
+        <v>0.634074</v>
       </c>
       <c r="D2" t="n">
-        <v>0.389014</v>
+        <v>0.35577</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.419404</v>
+        <v>0.410903</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.244684</v>
+        <v>0.243544</v>
       </c>
       <c r="D4" t="n">
-        <v>0.187885</v>
+        <v>0.18289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.309825</v>
+        <v>0.309842</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>500</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.277456</v>
+        <v>0.275302</v>
       </c>
       <c r="D5" t="n">
-        <v>0.209009</v>
+        <v>0.213667</v>
       </c>
       <c r="E5" t="n">
-        <v>0.374284</v>
+        <v>0.372892</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>tail_support_count</t>
+          <t>tail_support_at_or_beyond_var_incl_atom</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.634074</v>
+        <v>0.620194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35577</v>
+        <v>0.303016</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>500</v>
@@ -503,13 +503,13 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.410903</v>
+        <v>0.40983</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>500</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.243544</v>
+        <v>0.241226</v>
       </c>
       <c r="D4" t="n">
-        <v>0.18289</v>
+        <v>0.18145</v>
       </c>
       <c r="E4" t="n">
-        <v>0.309842</v>
+        <v>0.279656</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,16 +560,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.275302</v>
+        <v>0.273041</v>
       </c>
       <c r="D5" t="n">
-        <v>0.213667</v>
+        <v>0.204391</v>
       </c>
       <c r="E5" t="n">
-        <v>0.372892</v>
+        <v>0.313915</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>500</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.241226</v>
+        <v>0.238965</v>
       </c>
       <c r="D4" t="n">
-        <v>0.18145</v>
+        <v>0.180126</v>
       </c>
       <c r="E4" t="n">
-        <v>0.279656</v>
+        <v>0.281545</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.273041</v>
+        <v>0.273454</v>
       </c>
       <c r="D5" t="n">
-        <v>0.204391</v>
+        <v>0.203285</v>
       </c>
       <c r="E5" t="n">
-        <v>0.313915</v>
+        <v>0.316073</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.238965</v>
+        <v>0.238082</v>
       </c>
       <c r="D4" t="n">
-        <v>0.180126</v>
+        <v>0.179604</v>
       </c>
       <c r="E4" t="n">
-        <v>0.281545</v>
+        <v>0.282461</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.273454</v>
+        <v>0.273627</v>
       </c>
       <c r="D5" t="n">
-        <v>0.203285</v>
+        <v>0.204007</v>
       </c>
       <c r="E5" t="n">
-        <v>0.316073</v>
+        <v>0.317016</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -473,7 +473,7 @@
         <v>0.620194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.303016</v>
+        <v>0.235662</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.40983</v>
+        <v>0.389014</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.238082</v>
+        <v>0.246299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.179604</v>
+        <v>0.174754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.282461</v>
+        <v>0.308663</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.273627</v>
+        <v>0.308663</v>
       </c>
       <c r="D5" t="n">
-        <v>0.204007</v>
+        <v>0.194302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.317016</v>
+        <v>0.335817</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.246299</v>
+        <v>0.246428</v>
       </c>
       <c r="D4" t="n">
-        <v>0.174754</v>
+        <v>0.174766</v>
       </c>
       <c r="E4" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.308663</v>
+        <v>0.3087</v>
       </c>
       <c r="D5" t="n">
-        <v>0.194302</v>
+        <v>0.194276</v>
       </c>
       <c r="E5" t="n">
-        <v>0.335817</v>
+        <v>0.335732</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -473,7 +473,7 @@
         <v>0.620194</v>
       </c>
       <c r="D2" t="n">
-        <v>0.235662</v>
+        <v>0.229443</v>
       </c>
       <c r="E2" t="n">
         <v>0.76535</v>
@@ -503,7 +503,7 @@
         <v>0.711338</v>
       </c>
       <c r="D3" t="n">
-        <v>0.389014</v>
+        <v>0.371876</v>
       </c>
       <c r="E3" t="n">
         <v>0.838984</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.246428</v>
+        <v>0.249837</v>
       </c>
       <c r="D4" t="n">
-        <v>0.174766</v>
+        <v>0.172026</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3087</v>
+        <v>0.312595</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.3087</v>
+        <v>0.312595</v>
       </c>
       <c r="D5" t="n">
-        <v>0.194276</v>
+        <v>0.185775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.335732</v>
+        <v>0.339365</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.249837</v>
+        <v>0.250119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.172026</v>
+        <v>0.172381</v>
       </c>
       <c r="E4" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.312595</v>
+        <v>0.312875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.185775</v>
+        <v>0.185779</v>
       </c>
       <c r="E5" t="n">
-        <v>0.339365</v>
+        <v>0.33958</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>

--- a/vignettes/vignette-2/tail_support_bootstrap.xlsx
+++ b/vignettes/vignette-2/tail_support_bootstrap.xlsx
@@ -470,13 +470,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.620194</v>
+        <v>0.6049369999999999</v>
       </c>
       <c r="D2" t="n">
         <v>0.229443</v>
       </c>
       <c r="E2" t="n">
-        <v>0.76535</v>
+        <v>0.711338</v>
       </c>
       <c r="F2" t="n">
         <v>7</v>
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.711338</v>
+        <v>0.672434</v>
       </c>
       <c r="D3" t="n">
         <v>0.371876</v>
       </c>
       <c r="E3" t="n">
-        <v>0.838984</v>
+        <v>0.76535</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.250119</v>
+        <v>0.258309</v>
       </c>
       <c r="D4" t="n">
-        <v>0.172381</v>
+        <v>0.171823</v>
       </c>
       <c r="E4" t="n">
-        <v>0.312875</v>
+        <v>0.320405</v>
       </c>
       <c r="F4" t="n">
         <v>7</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.312875</v>
+        <v>0.320405</v>
       </c>
       <c r="D5" t="n">
-        <v>0.185779</v>
+        <v>0.18795</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33958</v>
+        <v>0.344667</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
